--- a/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
   <si>
     <t>AVAL</t>
   </si>
@@ -656,188 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="22" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="23" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>1062500</v>
+        <v>1119300</v>
       </c>
       <c r="E8" s="3">
+        <v>1065500</v>
+      </c>
+      <c r="F8" s="3">
         <v>939700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>890600</v>
       </c>
-      <c r="G8" s="3">
-        <v>865700</v>
-      </c>
       <c r="H8" s="3">
-        <v>779100</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+        <v>794300</v>
+      </c>
+      <c r="I8" s="3">
+        <v>779200</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>748900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>690000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>720200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>694700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>604100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>701300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>789000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1474500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1303200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1114500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>902300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>578700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>707300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>660300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>653500</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -910,53 +917,56 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1062500</v>
+        <v>1119300</v>
       </c>
       <c r="E10" s="3">
+        <v>1065500</v>
+      </c>
+      <c r="F10" s="3">
         <v>939700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>890600</v>
       </c>
-      <c r="G10" s="3">
-        <v>865700</v>
-      </c>
       <c r="H10" s="3">
-        <v>779100</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3">
+        <v>794300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>779200</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="3">
         <v>748900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>690000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>720200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>694700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>604100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>701300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>789000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -984,8 +994,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1012,8 +1025,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1086,8 +1100,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1160,50 +1177,53 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-8800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4700</v>
       </c>
-      <c r="G14" s="3">
-        <v>-3400</v>
-      </c>
       <c r="H14" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I14" s="3">
         <v>-1900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-2400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-23300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-3500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1228,88 +1248,94 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E15" s="3">
         <v>77900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>67700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>72600</v>
       </c>
-      <c r="G15" s="3">
-        <v>66600</v>
-      </c>
       <c r="H15" s="3">
+        <v>66500</v>
+      </c>
+      <c r="I15" s="3">
         <v>61600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>53700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>61900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>42000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>78300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>61100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>55900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>38500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>60400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-68600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-67700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-70400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-63200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-62600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-57200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-52400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-52900</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1333,156 +1359,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>656700</v>
+        <v>643700</v>
       </c>
       <c r="E17" s="3">
+        <v>659700</v>
+      </c>
+      <c r="F17" s="3">
         <v>639100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>539800</v>
       </c>
-      <c r="G17" s="3">
-        <v>524100</v>
-      </c>
       <c r="H17" s="3">
-        <v>477900</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3">
+        <v>500000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>478000</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3">
         <v>465800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>482000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>510900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>545600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>461800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>468700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>415300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1207500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>968100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>748600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>569900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>251700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>364100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>387300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>404100</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>475500</v>
+      </c>
+      <c r="E18" s="3">
         <v>405800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>300700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>350800</v>
       </c>
-      <c r="G18" s="3">
-        <v>341600</v>
-      </c>
       <c r="H18" s="3">
+        <v>294400</v>
+      </c>
+      <c r="I18" s="3">
         <v>301200</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3">
         <v>283100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>208000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>209300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>149100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>142200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>232500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>373700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>266900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>335100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>366000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>332400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>326900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>343200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>273000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>249400</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1509,156 +1542,163 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E20" s="3">
         <v>40300</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3">
         <v>37900</v>
       </c>
-      <c r="G20" s="3">
-        <v>34600</v>
-      </c>
       <c r="H20" s="3">
+        <v>30600</v>
+      </c>
+      <c r="I20" s="3">
         <v>28500</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>28500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>27400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>30200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>27900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>31100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>32500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-67700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>34200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>141100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>151400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-32600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>58500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>91300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>81900</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>521600</v>
+      </c>
+      <c r="E21" s="3">
         <v>443400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>368400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>385500</v>
       </c>
-      <c r="G21" s="3">
-        <v>373600</v>
-      </c>
       <c r="H21" s="3">
+        <v>330300</v>
+      </c>
+      <c r="I21" s="3">
         <v>334300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>53700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>316400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>222600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>257300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>197800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>170200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>239900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>401700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>267800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>437100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>577500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>547100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>383500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>482300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>438200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>406100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1701,8 +1741,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1725,162 +1765,171 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>440100</v>
+      </c>
+      <c r="E23" s="3">
         <v>367600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>309500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>317600</v>
       </c>
-      <c r="G23" s="3">
-        <v>310400</v>
-      </c>
       <c r="H23" s="3">
+        <v>266700</v>
+      </c>
+      <c r="I23" s="3">
         <v>274500</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K23" s="3">
         <v>256900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>184800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>181100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>160000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>117900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>194400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>341300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>199300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>369400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>507100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>483900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>294300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>401700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>364300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>331300</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>154500</v>
+      </c>
+      <c r="E24" s="3">
         <v>157800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>90100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>90700</v>
       </c>
-      <c r="G24" s="3">
-        <v>94000</v>
-      </c>
       <c r="H24" s="3">
+        <v>89300</v>
+      </c>
+      <c r="I24" s="3">
         <v>89400</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K24" s="3">
         <v>82100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>76200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>58500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>64800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>43600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>84000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>115000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>126300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>137000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>146700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>151900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>91000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>222600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>92500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>103300</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1953,156 +2002,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>285600</v>
+      </c>
+      <c r="E26" s="3">
         <v>209900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>219400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>226900</v>
       </c>
-      <c r="G26" s="3">
-        <v>216400</v>
-      </c>
       <c r="H26" s="3">
+        <v>177400</v>
+      </c>
+      <c r="I26" s="3">
         <v>185200</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K26" s="3">
         <v>174800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>108600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>122600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>95100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>74300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>110400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>226200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>72900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>232400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>360400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>332000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>203300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>179100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>271800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>228000</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E27" s="3">
         <v>91900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>91300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>132600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>121200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>86200</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="3">
         <v>99700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>49400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>29500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>39800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>91800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>95700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>102000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>175600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>151600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>37000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>111600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>138700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>204000</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2175,29 +2233,32 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-5900</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-50000</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>39000</v>
+      </c>
+      <c r="I29" s="3">
         <v>5900</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
@@ -2220,37 +2281,40 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-198200</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>263500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-73000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>59900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>60700</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-37700</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2323,8 +2387,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2397,156 +2464,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-39400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-40300</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3">
         <v>-37900</v>
       </c>
-      <c r="G32" s="3">
-        <v>-34600</v>
-      </c>
       <c r="H32" s="3">
+        <v>-30600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-28500</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-28500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-27400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-30200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-27900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-31100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-32500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>67700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-34200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-141100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-151400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>32600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-58500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-91300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-81900</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E33" s="3">
         <v>91900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>91300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>132600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>121200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>86200</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K33" s="3">
         <v>99700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>49400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>29500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>39800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>91800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-102500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>102000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>175600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>415100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-36100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>171500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>199400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>166300</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2619,161 +2695,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E35" s="3">
         <v>91900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>91300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>132600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>121200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>86200</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K35" s="3">
         <v>99700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>49400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>29500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>39800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>91800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-102500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>102000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>175600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>415100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-36100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>171500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>199400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>166300</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2800,8 +2885,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2828,201 +2914,208 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6392000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4477200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3624100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4485400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4453300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4563300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1650700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4245300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4302400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4474400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2171600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4543900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4600000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4175100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4087900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4503500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5574700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3937700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8794300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7896300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7478900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7377700</v>
       </c>
-      <c r="Y41" s="3">
-        <v>0</v>
-      </c>
       <c r="Z41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10295300</v>
+      </c>
+      <c r="E42" s="3">
         <v>7921500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5471500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7149900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6050900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4987800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3121600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4870700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4011700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4002400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3264500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3206000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3193300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2942300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>10928800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>11025600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>11083300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>9948200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>13366900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>11815200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>11196400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>10964900</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3872700</v>
+      </c>
+      <c r="E43" s="3">
         <v>3430100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2500000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3290400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3367500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7071500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2489200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3173600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3191500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3210800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2488500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6990700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6681600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6018200</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -3050,52 +3143,55 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E44" s="3">
         <v>11300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11700</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3">
         <v>17700</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3">
         <v>16600</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3124,53 +3220,56 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
         <v>3100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7359900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1667000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>20900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>942400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21600</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -3198,53 +3297,56 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20733400</v>
+      </c>
+      <c r="E46" s="3">
         <v>17849600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>20476100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15064500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13998200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16645300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11150500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12659000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11890800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12052200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11512700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14763900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14503000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13157200</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -3272,230 +3374,242 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11641200</v>
+      </c>
+      <c r="E47" s="3">
         <v>10838700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9978400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11016000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10153100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9905000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8547300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9068100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9308400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9766500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8391200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8642400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8157400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7163200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>341600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1373400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1269300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1045700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>281500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>236900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>222000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>203600</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
-      </c>
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3648600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2628900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2251500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1815600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1767500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1430200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1368000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1720500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1462300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1543600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1512300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1467800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1422500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1565600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1736500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1781500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1831400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1680800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2184100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1943400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1863500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1891300</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
-      </c>
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10657700</v>
+      </c>
+      <c r="E49" s="3">
         <v>9765700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9434100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9626000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9187200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4570500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8743800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9059700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9002400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9504600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9281000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4460400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4301500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3856100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4207500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4197300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4169400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3659200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5153000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4526400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4199400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4064600</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
-      </c>
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3568,8 +3682,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3642,82 +3759,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>140800</v>
+      </c>
+      <c r="E52" s="3">
         <v>109000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1179200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>137500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>131700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>442600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1055200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>128300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>394700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>415800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1242000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>398500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>407500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>131200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>466600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>34400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>37700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>35300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>473700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>31700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>26300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>52600</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3790,82 +3913,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>102027900</v>
+      </c>
+      <c r="E54" s="3">
         <v>92227100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>92539000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>87509100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>82208500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>78648100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>74351300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>76902800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>76549300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>79536600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>77744300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>73843200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>71426200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>64562300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>70941900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>71474100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>71788900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>62669800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>88056900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>77375100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>72292900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>70751400</v>
       </c>
-      <c r="Y54" s="3">
-        <v>0</v>
-      </c>
       <c r="Z54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3892,8 +4021,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3920,127 +4050,131 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65560600</v>
+      </c>
+      <c r="E57" s="3">
         <v>60188700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>55937600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>55028900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>52837300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>49547900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>46291200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>47795300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>48699600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>49877100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>47873400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45245700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>43193000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>38526900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>672900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>640100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>663800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>569900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>774800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>641300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>596400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>572900</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8597300</v>
+      </c>
+      <c r="E58" s="3">
         <v>6334200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9371200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6820100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4785800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4344400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6318300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5349900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4078600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4814100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6612400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4524100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>447800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>329000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4068,127 +4202,133 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2648800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2566500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4985500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1798000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1801800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>72900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>542300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1920500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2125900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2068800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>695700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1980000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1201900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>224300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1462100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1427000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1298500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>387400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1382400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1246800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1332200</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>77095700</v>
+      </c>
+      <c r="E60" s="3">
         <v>69330500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>70630900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>64017000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>59779100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53965200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53451400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55270700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>55199400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>57188000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>55477600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>51909900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>43669300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>40057800</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -4216,156 +4356,165 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12771800</v>
+      </c>
+      <c r="E61" s="3">
         <v>11838500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>9367500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12922500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12363400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12255200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10430900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11919900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12113400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>12663900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10918200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>12743000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16037400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>15129400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15126900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>14763300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>15120000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>12389300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15026400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>12193300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>11352000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11073300</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>726900</v>
+      </c>
+      <c r="E62" s="3">
         <v>635400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>692400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>610500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>771500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3049100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>563400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>518100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>502800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>512700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>759600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>567900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2838100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2654000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1621000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>390900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>404600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>393900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1462300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>348700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>332700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>339500</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
-      </c>
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4438,8 +4587,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4512,8 +4664,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4586,82 +4741,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91913600</v>
+      </c>
+      <c r="E66" s="3">
         <v>83044600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>83325100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>78694100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>73968000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>70867300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>66830700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>69037700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>68890100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>71482700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>69607900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>66241000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>64054500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>58032800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>66989800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>67282400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>67519700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>58774500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>82533700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>72460600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>67787200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>66472500</v>
       </c>
-      <c r="Y66" s="3">
-        <v>0</v>
-      </c>
       <c r="Z66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4688,8 +4849,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4762,8 +4924,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4836,8 +5001,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4910,8 +5078,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4984,82 +5155,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2735800</v>
+      </c>
+      <c r="E72" s="3">
         <v>2411200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2450800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2266200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2048300</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>1851300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1893300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1808900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1886400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1995800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1888900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1817500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1604700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1924400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2087700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2065500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2032800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3212000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2777700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2486200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2287600</v>
       </c>
-      <c r="Y72" s="3">
-        <v>0</v>
-      </c>
       <c r="Z72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5132,8 +5309,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5206,8 +5386,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5280,82 +5463,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5403300</v>
+      </c>
+      <c r="E76" s="3">
         <v>4862400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4891900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4685700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4349100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4094600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3957600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4170300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4042400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4263900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4332100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4049300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3945700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3494200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3952100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4191600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4269200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3895300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5523300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4914500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4505700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4279000</v>
       </c>
-      <c r="Y76" s="3">
-        <v>0</v>
-      </c>
       <c r="Z76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5428,161 +5617,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>168000</v>
+      </c>
+      <c r="E81" s="3">
         <v>91900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>91300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>132600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>121200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>86200</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K81" s="3">
         <v>99700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>49400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>29500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>39800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>91800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-102500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>102000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>175600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>415100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-36100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>171500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>199400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>166300</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5609,82 +5807,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E83" s="3">
         <v>34300</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3">
         <v>78000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>75000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>78300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>36500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>67700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>60400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>58900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>64900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>70100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>68600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>67700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>70400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>63200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>89100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>80700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>73900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>74800</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5757,8 +5959,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5831,8 +6036,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5905,8 +6113,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5979,8 +6190,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6053,82 +6267,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1380600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1074800</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3">
         <v>-89200</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3">
+        <v>-1087400</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1314000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
         <v>203900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1846100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1105100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-345700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>88800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-847100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1043600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-998500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-333000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1538000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-489300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>495500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-21700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>505500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>321100</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6155,82 +6375,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-40200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27500</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3">
         <v>-36400</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H91" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-30500</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K91" s="3">
         <v>-31500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-42200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-38000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-59700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-33700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-37900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-482508000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-281054000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-238582000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-143769000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-489803000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-299606000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6303,8 +6527,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6377,82 +6604,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-589300</v>
+      </c>
+      <c r="E94" s="3">
         <v>633800</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3">
         <v>-369900</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H94" s="3">
+        <v>41900</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
         <v>242200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>101900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-458700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-228900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>54900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>564200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>662200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>345800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>47900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4161400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-522800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>67100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-178900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-814100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6479,82 +6712,86 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E96" s="3">
         <v>44100</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3">
         <v>41100</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H96" s="3">
+        <v>39600</v>
+      </c>
+      <c r="I96" s="3">
         <v>33600</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K96" s="3">
         <v>33900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>34200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>66100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>65800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>63000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>61100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-28600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-72000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-72100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-66000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-62900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-69500</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6627,8 +6864,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6701,8 +6941,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6775,226 +7018,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1627600</v>
+      </c>
+      <c r="E100" s="3">
         <v>1962700</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3">
         <v>460300</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3">
+        <v>1224800</v>
+      </c>
+      <c r="I100" s="3">
         <v>1961700</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
         <v>-523100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1660900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1521100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>808000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-27500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>934200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1058000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-573100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1186700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-276100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-89700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-18500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-57600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-229100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>17700</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-302800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-136500</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3">
         <v>42300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>259300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>35100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-387300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-33400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-173700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-82900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>579300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>275700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-128900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>673900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>317100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-116100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>226000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>73500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>707700</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-351500</v>
+      </c>
+      <c r="E102" s="3">
         <v>1196300</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-140700</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>-123500</v>
+      </c>
+      <c r="I102" s="3">
         <v>510200</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-34600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>176000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>55600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-201100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-31700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>495800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-235500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-856800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1308800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4856600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>180100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>61300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>101100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>232400</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>
